--- a/backend/data/financials_by_company/000636.SZ.xlsx
+++ b/backend/data/financials_by_company/000636.SZ.xlsx
@@ -4017,187 +4017,187 @@
       </c>
       <c r="DG1" t="inlineStr">
         <is>
+          <t>exchange</t>
+        </is>
+      </c>
+      <c r="DH1" t="inlineStr">
+        <is>
+          <t>messageBoardId</t>
+        </is>
+      </c>
+      <c r="DI1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneName</t>
+        </is>
+      </c>
+      <c r="DJ1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneShortName</t>
+        </is>
+      </c>
+      <c r="DK1" t="inlineStr">
+        <is>
+          <t>gmtOffSetMilliseconds</t>
+        </is>
+      </c>
+      <c r="DL1" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="DM1" t="inlineStr">
+        <is>
+          <t>esgPopulated</t>
+        </is>
+      </c>
+      <c r="DN1" t="inlineStr">
+        <is>
           <t>corporateActions</t>
         </is>
       </c>
-      <c r="DH1" t="inlineStr">
+      <c r="DO1" t="inlineStr">
         <is>
           <t>regularMarketTime</t>
         </is>
       </c>
-      <c r="DI1" t="inlineStr">
-        <is>
-          <t>exchange</t>
-        </is>
-      </c>
-      <c r="DJ1" t="inlineStr">
-        <is>
-          <t>messageBoardId</t>
-        </is>
-      </c>
-      <c r="DK1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneName</t>
-        </is>
-      </c>
-      <c r="DL1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneShortName</t>
-        </is>
-      </c>
-      <c r="DM1" t="inlineStr">
-        <is>
-          <t>gmtOffSetMilliseconds</t>
-        </is>
-      </c>
-      <c r="DN1" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="DO1" t="inlineStr">
-        <is>
-          <t>esgPopulated</t>
-        </is>
-      </c>
       <c r="DP1" t="inlineStr">
         <is>
+          <t>shortName</t>
+        </is>
+      </c>
+      <c r="DQ1" t="inlineStr">
+        <is>
           <t>longName</t>
         </is>
       </c>
-      <c r="DQ1" t="inlineStr">
-        <is>
-          <t>shortName</t>
-        </is>
-      </c>
       <c r="DR1" t="inlineStr">
         <is>
+          <t>regularMarketChangePercent</t>
+        </is>
+      </c>
+      <c r="DS1" t="inlineStr">
+        <is>
+          <t>regularMarketPrice</t>
+        </is>
+      </c>
+      <c r="DT1" t="inlineStr">
+        <is>
+          <t>epsTrailingTwelveMonths</t>
+        </is>
+      </c>
+      <c r="DU1" t="inlineStr">
+        <is>
+          <t>epsForward</t>
+        </is>
+      </c>
+      <c r="DV1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChange</t>
+        </is>
+      </c>
+      <c r="DW1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="DX1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChange</t>
+        </is>
+      </c>
+      <c r="DY1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="DZ1" t="inlineStr">
+        <is>
+          <t>sourceInterval</t>
+        </is>
+      </c>
+      <c r="EA1" t="inlineStr">
+        <is>
+          <t>exchangeDataDelayedBy</t>
+        </is>
+      </c>
+      <c r="EB1" t="inlineStr">
+        <is>
+          <t>cryptoTradeable</t>
+        </is>
+      </c>
+      <c r="EC1" t="inlineStr">
+        <is>
           <t>hasPrePostMarketData</t>
         </is>
       </c>
-      <c r="DS1" t="inlineStr">
+      <c r="ED1" t="inlineStr">
         <is>
           <t>firstTradeDateMilliseconds</t>
         </is>
       </c>
-      <c r="DT1" t="inlineStr">
+      <c r="EE1" t="inlineStr">
         <is>
           <t>regularMarketChange</t>
         </is>
       </c>
-      <c r="DU1" t="inlineStr">
+      <c r="EF1" t="inlineStr">
         <is>
           <t>regularMarketDayRange</t>
         </is>
       </c>
-      <c r="DV1" t="inlineStr">
+      <c r="EG1" t="inlineStr">
         <is>
           <t>fullExchangeName</t>
         </is>
       </c>
-      <c r="DW1" t="inlineStr">
+      <c r="EH1" t="inlineStr">
         <is>
           <t>averageDailyVolume3Month</t>
         </is>
       </c>
-      <c r="DX1" t="inlineStr">
+      <c r="EI1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekLowChange</t>
         </is>
       </c>
-      <c r="DY1" t="inlineStr">
+      <c r="EJ1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekLowChangePercent</t>
         </is>
       </c>
-      <c r="DZ1" t="inlineStr">
+      <c r="EK1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekRange</t>
         </is>
       </c>
-      <c r="EA1" t="inlineStr">
+      <c r="EL1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekHighChange</t>
         </is>
       </c>
-      <c r="EB1" t="inlineStr">
+      <c r="EM1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekHighChangePercent</t>
         </is>
       </c>
-      <c r="EC1" t="inlineStr">
+      <c r="EN1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekChangePercent</t>
         </is>
       </c>
-      <c r="ED1" t="inlineStr">
+      <c r="EO1" t="inlineStr">
         <is>
           <t>earningsTimestampStart</t>
         </is>
       </c>
-      <c r="EE1" t="inlineStr">
+      <c r="EP1" t="inlineStr">
         <is>
           <t>earningsTimestampEnd</t>
         </is>
       </c>
-      <c r="EF1" t="inlineStr">
-        <is>
-          <t>epsTrailingTwelveMonths</t>
-        </is>
-      </c>
-      <c r="EG1" t="inlineStr">
-        <is>
-          <t>epsForward</t>
-        </is>
-      </c>
-      <c r="EH1" t="inlineStr">
+      <c r="EQ1" t="inlineStr">
         <is>
           <t>marketState</t>
-        </is>
-      </c>
-      <c r="EI1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChange</t>
-        </is>
-      </c>
-      <c r="EJ1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="EK1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChange</t>
-        </is>
-      </c>
-      <c r="EL1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="EM1" t="inlineStr">
-        <is>
-          <t>sourceInterval</t>
-        </is>
-      </c>
-      <c r="EN1" t="inlineStr">
-        <is>
-          <t>exchangeDataDelayedBy</t>
-        </is>
-      </c>
-      <c r="EO1" t="inlineStr">
-        <is>
-          <t>cryptoTradeable</t>
-        </is>
-      </c>
-      <c r="EP1" t="inlineStr">
-        <is>
-          <t>regularMarketChangePercent</t>
-        </is>
-      </c>
-      <c r="EQ1" t="inlineStr">
-        <is>
-          <t>regularMarketPrice</t>
         </is>
       </c>
       <c r="ER1" t="inlineStr">
@@ -4302,34 +4302,34 @@
         <v>2</v>
       </c>
       <c r="U2" t="n">
-        <v>74.59999999999999</v>
+        <v>66.95999999999999</v>
       </c>
       <c r="V2" t="n">
-        <v>71.5</v>
+        <v>77.5</v>
       </c>
       <c r="W2" t="n">
-        <v>70.33</v>
+        <v>61.27</v>
       </c>
       <c r="X2" t="n">
-        <v>75.75</v>
+        <v>68.68000000000001</v>
       </c>
       <c r="Y2" t="n">
-        <v>74.59999999999999</v>
+        <v>66.95999999999999</v>
       </c>
       <c r="Z2" t="n">
-        <v>71.5</v>
+        <v>77.5</v>
       </c>
       <c r="AA2" t="n">
-        <v>70.33</v>
+        <v>61.27</v>
       </c>
       <c r="AB2" t="n">
-        <v>75.75</v>
+        <v>68.68000000000001</v>
       </c>
       <c r="AC2" t="n">
         <v>0.15</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="AE2" t="n">
         <v>1752192000</v>
@@ -4341,67 +4341,67 @@
         <v>0.74</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.816</v>
+        <v>1.774</v>
       </c>
       <c r="AI2" t="n">
-        <v>270.2963</v>
+        <v>234.18518</v>
       </c>
       <c r="AJ2" t="n">
-        <v>140.34616</v>
+        <v>121.59616</v>
       </c>
       <c r="AK2" t="n">
-        <v>156696183</v>
+        <v>90675564</v>
       </c>
       <c r="AL2" t="n">
-        <v>156696183</v>
+        <v>90675564</v>
       </c>
       <c r="AM2" t="n">
-        <v>105589238</v>
+        <v>118298835</v>
       </c>
       <c r="AN2" t="n">
-        <v>169508529</v>
+        <v>123078521</v>
       </c>
       <c r="AO2" t="n">
-        <v>169508529</v>
+        <v>123078521</v>
       </c>
       <c r="AP2" t="n">
-        <v>72.81</v>
+        <v>63.21</v>
       </c>
       <c r="AQ2" t="n">
-        <v>72.81999999999999</v>
+        <v>63.23</v>
       </c>
       <c r="AR2" t="n">
-        <v>84438827008</v>
+        <v>73157943296</v>
       </c>
       <c r="AS2" t="n">
-        <v>86313185540</v>
+        <v>86081782898</v>
       </c>
       <c r="AT2" t="n">
-        <v>12.91</v>
+        <v>13.59</v>
       </c>
       <c r="AU2" t="n">
-        <v>76.09999999999999</v>
+        <v>84</v>
       </c>
       <c r="AV2" t="n">
-        <v>76.09999999999999</v>
+        <v>84</v>
       </c>
       <c r="AW2" t="n">
         <v>1.069958</v>
       </c>
       <c r="AX2" t="n">
-        <v>14.079767</v>
+        <v>12.198734</v>
       </c>
       <c r="AY2" t="n">
-        <v>38.1908</v>
+        <v>47.6744</v>
       </c>
       <c r="AZ2" t="n">
-        <v>23.28315</v>
+        <v>25.91935</v>
       </c>
       <c r="BA2" t="n">
         <v>0.1</v>
       </c>
       <c r="BB2" t="n">
-        <v>0.0013404826</v>
+        <v>0.001493429</v>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
@@ -4412,13 +4412,13 @@
         <v>0</v>
       </c>
       <c r="BE2" t="n">
-        <v>80080609280</v>
+        <v>68892573696</v>
       </c>
       <c r="BF2" t="n">
         <v>0.05124</v>
       </c>
       <c r="BG2" t="n">
-        <v>770425067</v>
+        <v>771790581</v>
       </c>
       <c r="BH2" t="n">
         <v>1157013211</v>
@@ -4427,7 +4427,7 @@
         <v>0.30825</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.105340004</v>
+        <v>0.08287</v>
       </c>
       <c r="BK2" t="n">
         <v>1157013211</v>
@@ -4436,7 +4436,7 @@
         <v>10.878</v>
       </c>
       <c r="BM2" t="n">
-        <v>6.708954</v>
+        <v>5.8126493</v>
       </c>
       <c r="BN2" t="n">
         <v>1767139200</v>
@@ -4468,16 +4468,16 @@
         <v>1144281600</v>
       </c>
       <c r="BW2" t="n">
-        <v>13.353</v>
+        <v>11.488</v>
       </c>
       <c r="BX2" t="n">
-        <v>91.79000000000001</v>
+        <v>78.96599999999999</v>
       </c>
       <c r="BY2" t="n">
-        <v>4.6558</v>
+        <v>3.8911614</v>
       </c>
       <c r="BZ2" t="n">
-        <v>0.24487448</v>
+        <v>0.20116603</v>
       </c>
       <c r="CA2" t="n">
         <v>0.15</v>
@@ -4491,7 +4491,7 @@
         </is>
       </c>
       <c r="CD2" t="n">
-        <v>72.98</v>
+        <v>63.23</v>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
@@ -4595,138 +4595,138 @@
       </c>
       <c r="DG2" t="inlineStr">
         <is>
+          <t>SHZ</t>
+        </is>
+      </c>
+      <c r="DH2" t="inlineStr">
+        <is>
+          <t>finmb_28456</t>
+        </is>
+      </c>
+      <c r="DI2" t="inlineStr">
+        <is>
+          <t>Asia/Shanghai</t>
+        </is>
+      </c>
+      <c r="DJ2" t="inlineStr">
+        <is>
+          <t>CST</t>
+        </is>
+      </c>
+      <c r="DK2" t="n">
+        <v>28800000</v>
+      </c>
+      <c r="DL2" t="inlineStr">
+        <is>
+          <t>cn_market</t>
+        </is>
+      </c>
+      <c r="DM2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DN2" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="DH2" t="n">
-        <v>1782111867</v>
-      </c>
-      <c r="DI2" t="inlineStr">
-        <is>
-          <t>SHZ</t>
-        </is>
-      </c>
-      <c r="DJ2" t="inlineStr">
-        <is>
-          <t>finmb_28456</t>
-        </is>
-      </c>
-      <c r="DK2" t="inlineStr">
-        <is>
-          <t>Asia/Shanghai</t>
-        </is>
-      </c>
-      <c r="DL2" t="inlineStr">
-        <is>
-          <t>CST</t>
-        </is>
-      </c>
-      <c r="DM2" t="n">
-        <v>28800000</v>
-      </c>
-      <c r="DN2" t="inlineStr">
-        <is>
-          <t>cn_market</t>
-        </is>
-      </c>
-      <c r="DO2" t="b">
+      <c r="DO2" t="n">
+        <v>1783062249</v>
+      </c>
+      <c r="DP2" t="inlineStr">
+        <is>
+          <t>FENGHUA ADVANCE TECHNOLOGY HLDG</t>
+        </is>
+      </c>
+      <c r="DQ2" t="inlineStr">
+        <is>
+          <t>Guangdong Fenghua Advanced Technology (Holding) Co., Ltd.</t>
+        </is>
+      </c>
+      <c r="DR2" t="n">
+        <v>-5.570489</v>
+      </c>
+      <c r="DS2" t="n">
+        <v>63.23</v>
+      </c>
+      <c r="DT2" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="DU2" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="DV2" t="n">
+        <v>15.555599</v>
+      </c>
+      <c r="DW2" t="n">
+        <v>0.3262883</v>
+      </c>
+      <c r="DX2" t="n">
+        <v>37.31065</v>
+      </c>
+      <c r="DY2" t="n">
+        <v>1.4394902</v>
+      </c>
+      <c r="DZ2" t="n">
+        <v>15</v>
+      </c>
+      <c r="EA2" t="n">
+        <v>15</v>
+      </c>
+      <c r="EB2" t="b">
         <v>0</v>
       </c>
-      <c r="DP2" t="inlineStr">
-        <is>
-          <t>Guangdong Fenghua Advanced Technology (Holding) Co., Ltd.</t>
-        </is>
-      </c>
-      <c r="DQ2" t="inlineStr">
-        <is>
-          <t>FENGHUA ADVANCE TECHNOLOGY HLDG</t>
-        </is>
-      </c>
-      <c r="DR2" t="b">
+      <c r="EC2" t="b">
         <v>0</v>
       </c>
-      <c r="DS2" t="n">
+      <c r="ED2" t="n">
         <v>849231000000</v>
       </c>
-      <c r="DT2" t="n">
-        <v>-1.6199951</v>
-      </c>
-      <c r="DU2" t="inlineStr">
-        <is>
-          <t>70.33 - 75.75</t>
-        </is>
-      </c>
-      <c r="DV2" t="inlineStr">
+      <c r="EE2" t="n">
+        <v>-3.7299995</v>
+      </c>
+      <c r="EF2" t="inlineStr">
+        <is>
+          <t>61.27 - 68.68</t>
+        </is>
+      </c>
+      <c r="EG2" t="inlineStr">
         <is>
           <t>Shenzhen</t>
         </is>
       </c>
-      <c r="DW2" t="n">
-        <v>105589238</v>
-      </c>
-      <c r="DX2" t="n">
-        <v>60.070004</v>
-      </c>
-      <c r="DY2" t="n">
-        <v>4.6529827</v>
-      </c>
-      <c r="DZ2" t="inlineStr">
-        <is>
-          <t>12.91 - 76.1</t>
-        </is>
-      </c>
-      <c r="EA2" t="n">
-        <v>-3.119995</v>
-      </c>
-      <c r="EB2" t="n">
-        <v>-0.040998623</v>
-      </c>
-      <c r="EC2" t="n">
-        <v>465.58</v>
-      </c>
-      <c r="ED2" t="n">
+      <c r="EH2" t="n">
+        <v>118298835</v>
+      </c>
+      <c r="EI2" t="n">
+        <v>49.64</v>
+      </c>
+      <c r="EJ2" t="n">
+        <v>3.6526856</v>
+      </c>
+      <c r="EK2" t="inlineStr">
+        <is>
+          <t>13.59 - 84.0</t>
+        </is>
+      </c>
+      <c r="EL2" t="n">
+        <v>-20.77</v>
+      </c>
+      <c r="EM2" t="n">
+        <v>-0.24726191</v>
+      </c>
+      <c r="EN2" t="n">
+        <v>389.11615</v>
+      </c>
+      <c r="EO2" t="n">
         <v>1651229940</v>
       </c>
-      <c r="EE2" t="n">
+      <c r="EP2" t="n">
         <v>1651492800</v>
       </c>
-      <c r="EF2" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="EG2" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="EH2" t="inlineStr">
-        <is>
-          <t>PREPRE</t>
-        </is>
-      </c>
-      <c r="EI2" t="n">
-        <v>34.789204</v>
-      </c>
-      <c r="EJ2" t="n">
-        <v>0.9109315</v>
-      </c>
-      <c r="EK2" t="n">
-        <v>49.696854</v>
-      </c>
-      <c r="EL2" t="n">
-        <v>2.1344557</v>
-      </c>
-      <c r="EM2" t="n">
-        <v>15</v>
-      </c>
-      <c r="EN2" t="n">
-        <v>15</v>
-      </c>
-      <c r="EO2" t="b">
-        <v>0</v>
-      </c>
-      <c r="EP2" t="n">
-        <v>-2.1715753</v>
-      </c>
-      <c r="EQ2" t="n">
-        <v>72.98</v>
+      <c r="EQ2" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
       </c>
       <c r="ER2" t="inlineStr"/>
     </row>
